--- a/assets/data/marktplaats_pianos_emotional_seller_descriptions.xlsx
+++ b/assets/data/marktplaats_pianos_emotional_seller_descriptions.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Piano listings" sheetId="1" r:id="Rcbce416ca84a4fe3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="R0c47a2427d5e430b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Piano listings" sheetId="1" r:id="R03fe4f0658e44e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" r:id="Rbdfa09d75fc84f14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -337,7 +337,7 @@
         <x:v>Price</x:v>
       </x:c>
       <x:c r="C1" s="5" t="str">
-        <x:v>Image links</x:v>
+        <x:v>Image links removed</x:v>
       </x:c>
       <x:c r="D1" s="5" t="str">
         <x:v>Additional info</x:v>
@@ -349,7 +349,7 @@
         <x:v>Description source</x:v>
       </x:c>
       <x:c r="G1" s="5" t="str">
-        <x:v>Listing URL</x:v>
+        <x:v>Listing URL removed</x:v>
       </x:c>
       <x:c r="H1" s="10" t="str">
         <x:v>Seller tone</x:v>
@@ -368,9 +368,7 @@
       <x:c r="B2" s="14" t="str">
         <x:v>See description</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/41/41b0451c-5e40-4ba7-89ed-598d7707db58?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C2" s="14" t="str"/>
       <x:c r="D2" s="14" t="str">
         <x:v>Used · Black · Upright / grand collection · Yamaha acoustic &amp; Silent pianos | Full warranty | Large rotating stock</x:v>
       </x:c>
@@ -378,11 +376,9 @@
         <x:v>A long-running Yamaha specialist advertises a large rotating stock of acoustic uprights, Silent pianos and grand pianos. The listing highlights more than 45 years in business, full warranty on Yamaha acoustic and Silent instruments, workshop inspection before delivery, and a broad range of U1/U3, UX, YU and grand-piano models. Prices vary by instrument and the seller recommends checking current stock because availability changes frequently.</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G2" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1111742037-grote-collectie-yamaha-pianos-silent-pianos-en-vleugels</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str"/>
       <x:c r="H2" s="14" t="str">
         <x:v>Proud / established specialist</x:v>
       </x:c>
@@ -395,14 +391,12 @@
     </x:row>
     <x:row r="3" ht="116" customHeight="1">
       <x:c r="A3" s="14" t="str">
-        <x:v>Yamaha U3M piano | Actieprijs | SOUMAN.NL</x:v>
+        <x:v>Yamaha U3M piano | Actieprijs | Northstar Music</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
         <x:v>€ 3.950,-</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/b5/b5b1c082-e677-4480-9e5d-248b00726901?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C3" s="14" t="str"/>
       <x:c r="D3" s="14" t="str">
         <x:v>Yamaha U3M · Acoustic upright · Black high gloss · Like new | 12-year warranty | Free ground-floor transport, bench and floor protectors</x:v>
       </x:c>
@@ -410,11 +404,9 @@
         <x:v>A professionally prepared Yamaha U3M acoustic upright in black high gloss. The seller describes the U3 series as popular with teachers, schools and musicians because of its reliability, stable tuning and strong, transparent tone with warm bass and bright upper register. The instrument has been adjusted by the shop and is described as technically in near-new condition. The package includes a 12-year warranty, ground-floor delivery, an adjustable bench and floor protectors.</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1526912886-yamaha-u3m-piano-actieprijs-souman-nl</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str"/>
       <x:c r="H3" s="14" t="str">
         <x:v>Confident / teacher-approved</x:v>
       </x:c>
@@ -427,14 +419,12 @@
     </x:row>
     <x:row r="4" ht="116" customHeight="1">
       <x:c r="A4" s="14" t="str">
-        <x:v>Yamaha U300SX Silent piano | Actieprijs | SOUMAN.NL</x:v>
+        <x:v>Yamaha U300SX Silent piano | Actieprijs | Northstar Music</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
         <x:v>€ 6.950,-</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/8f/8fb41a8f-37fa-4546-a200-8d56d1b3c225?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C4" s="14" t="str"/>
       <x:c r="D4" s="14" t="str">
         <x:v>Yamaha U300SX Silent · Black high gloss · Like new · Acoustic + digital silent system | Workshop prepared</x:v>
       </x:c>
@@ -442,11 +432,9 @@
         <x:v>A Yamaha U300SX Silent upright combining a full acoustic mechanism with headphone practice. The shop presents it as one of the more popular Silent Yamaha models, suitable for classical or pop playing and for homes where quiet practice matters. It has been prepared by the seller's technicians and is described as technically near new, with the power and clarity associated with Yamaha's taller U-series uprights.</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G4" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1526912894-yamaha-u300sx-silent-piano-actieprijs-souman-nl</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str"/>
       <x:c r="H4" s="14" t="str">
         <x:v>Enthusiastic / practical</x:v>
       </x:c>
@@ -464,9 +452,7 @@
       <x:c r="B5" s="14" t="str">
         <x:v>€ 34.950,-</x:v>
       </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/2f/2f44d2fb-e2ba-41d9-b301-e81b66fc93a6?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C5" s="14" t="str"/>
       <x:c r="D5" s="14" t="str">
         <x:v>2024 · Yamaha C3XE Espressivo · 186 cm grand · Black high gloss · Like new · Imported from Japan</x:v>
       </x:c>
@@ -474,11 +460,9 @@
         <x:v>A very young 2024 Yamaha C3XE Espressivo grand imported from Japan and presented as nearly new. The Espressivo version receives more refined voicing, premium hammer work and additional technician attention compared with a standard C3X. At 186 cm it is positioned as a versatile mid-size grand with substantial bass, a warm middle register and clear treble, suitable for a serious home, studio or professional setting.</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G5" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1526912904-yamaha-c3xe-espressivo-vleugel-bouwjaar-2024</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str"/>
       <x:c r="H5" s="14" t="str">
         <x:v>Excited / connoisseur</x:v>
       </x:c>
@@ -491,14 +475,12 @@
     </x:row>
     <x:row r="6" ht="116" customHeight="1">
       <x:c r="A6" s="14" t="str">
-        <x:v>Best price/quality Roland digital piano? SOUMAN.NL</x:v>
+        <x:v>Best price/quality Roland digital piano? Northstar Music</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>See description</x:v>
       </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/36/36b60f8d-2f37-4b63-9f32-5ae84b9b93e2?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C6" s="14" t="str"/>
       <x:c r="D6" s="14" t="str">
         <x:v>New Roland digital-piano range · FP-10, FP-30X, FP-60X, FP-90X, F107, RP107 and others | Full warranty | Free shipping</x:v>
       </x:c>
@@ -506,11 +488,9 @@
         <x:v>A dealer listing for a broad selection of new Roland digital pianos rather than one specific instrument. The seller keeps popular stage and home models available for side-by-side comparison, including the FP-10, FP-30X, FP-E50, FP-60X, FP-90X, F107 and RP107. Advice, demonstrations, full warranty and free shipping are emphasized; exact pricing depends on the selected model.</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G6" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1462408035-opzoek-naar-de-beste-prijs-kwaliteit-roland-piano-souman-nl</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str"/>
       <x:c r="H6" s="14" t="str">
         <x:v>Helpful / sales-oriented</x:v>
       </x:c>
@@ -523,14 +503,12 @@
     </x:row>
     <x:row r="7" ht="116" customHeight="1">
       <x:c r="A7" s="14" t="str">
-        <x:v>45 years - piano specialist Arnhem-Nijmegen region</x:v>
+        <x:v>45 years - piano specialist the local region region</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
         <x:v>See description</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/4b/4b7330a2-e188-44a3-a17f-46c94d9fc9b4?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C7" s="14" t="str"/>
       <x:c r="D7" s="14" t="str">
         <x:v>Schimmel &amp; Yamaha collection · Acoustic and Silent systems · Mostly like new | Workshop business | Service area around Elst</x:v>
       </x:c>
@@ -538,11 +516,9 @@
         <x:v>A long-established independent piano shop advertises a changing collection of Schimmel and Yamaha uprights, including conventional acoustic instruments and original or aftermarket silent systems. The seller stresses an artisan workshop approach rather than promotional gimmicks, with a service radius of roughly 40 km around Elst. Stock and prices vary by individual instrument.</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G7" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2318125149-al-45-jaar-de-pianozaak-van-regio-arnhem-nijmegen</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str"/>
       <x:c r="H7" s="14" t="str">
         <x:v>Old-school / candid craftsman</x:v>
       </x:c>
@@ -560,9 +536,7 @@
       <x:c r="B8" s="14" t="str">
         <x:v>See description</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/e263eadf-581e-45de-b1b8-a2de26280019?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C8" s="14" t="str"/>
       <x:c r="D8" s="14" t="str">
         <x:v>Schimmel 118/116/114 collection · Various years and finishes · Acoustic and Silent options | Prices roughly €2,650-€9,450 depending on piano</x:v>
       </x:c>
@@ -570,11 +544,9 @@
         <x:v>A dealer collection centered on Schimmel 118-series uprights, with several heights, years, finishes and silent-system configurations. The live stock list includes black high-gloss, white, oak and structured finishes, with examples ranging from older study instruments to newer premium C-series models. Pricing varies significantly by year, condition and silent equipment.</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2344765461-8x-schimmel-118-t-deutsche-perfektion-zwart-wit-bruin</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str"/>
       <x:c r="H8" s="14" t="str">
         <x:v>Specialist / understated pride</x:v>
       </x:c>
@@ -592,9 +564,7 @@
       <x:c r="B9" s="14" t="str">
         <x:v>€ 2.495,-</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/494f5d2a-1dc7-43ac-9353-2a731084bbae?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C9" s="14" t="str"/>
       <x:c r="D9" s="14" t="str">
         <x:v>Used · Yamaha P-155 digital piano + portable high-gloss grand shell + upright shells | Stage/theatre/event setup | Wheels and transport-friendly construction</x:v>
       </x:c>
@@ -602,11 +572,9 @@
         <x:v>A very unusual complete stage set consisting of a Yamaha P-155 digital piano plus portable piano shells that let the same instrument appear as a stage piano, low or high upright, or grand piano. The shells were previously used for concerts, theatre and events and are designed to provide acoustic-piano stage presence without the transport burden of a real grand. The grand shell has wheels and detachable sections to reduce transport size.</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435844160-portable-vleugelshell-hoge-lage-pianoshell-yamaha-p-155</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str"/>
       <x:c r="H9" s="14" t="str">
         <x:v>Nostalgic / creative</x:v>
       </x:c>
@@ -624,9 +592,7 @@
       <x:c r="B10" s="14" t="str">
         <x:v>€ 8.990,-</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/558a4cdc-c267-41f3-8f9d-caba85f6203a?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C10" s="14" t="str"/>
       <x:c r="D10" s="14" t="str">
         <x:v>Schimmel 116 · Black high gloss · Like new · New Genio Premium Silent system | Delivery, tuning and 5-year warranty included</x:v>
       </x:c>
@@ -634,11 +600,9 @@
         <x:v>A 116 cm Schimmel upright in black high gloss fitted with a new Genio Premium Silent system. The seller positions it as a combination of the warm, balanced tone and refined action associated with German Schimmel uprights and modern headphone practice. The package includes mechanical service, tuning before and after delivery, ground-floor delivery and a five-year warranty.</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2352887857-prachtige-schimmel-116cm-hoog-nieuw-silentsysteem</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str"/>
       <x:c r="H10" s="14" t="str">
         <x:v>Premium / reassuring</x:v>
       </x:c>
@@ -656,9 +620,7 @@
       <x:c r="B11" s="14" t="str">
         <x:v>€ 3.250,-</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/24a52566-6634-454f-bc24-8dab2356120b?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C11" s="14" t="str"/>
       <x:c r="D11" s="14" t="str">
         <x:v>1995 · Kawai XO-5 · Made in Japan · 88 keys · 3 pedals · Black high gloss | Mechanism in excellent condition</x:v>
       </x:c>
@@ -666,11 +628,9 @@
         <x:v>A Japanese-built 1995 Kawai XO-5 upright in high-gloss black. The seller describes it as very clean and well maintained, with minimal cabinet wear, a mechanism in excellent condition, smooth accurate touch and a warm but clear tone. It has 88 keys, three pedals and is currently located on the ground floor for easier collection.</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2430059162-kawai-xo-5-piano-hoogglans-zwart-1995</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str"/>
       <x:c r="H11" s="14" t="str">
         <x:v>Proud / quality-focused</x:v>
       </x:c>
@@ -688,9 +648,7 @@
       <x:c r="B12" s="14" t="str">
         <x:v>€ 3.900,-</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/17d082d5-b9ae-41b5-b23e-df0ea0913bf0?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C12" s="14" t="str"/>
       <x:c r="D12" s="14" t="str">
         <x:v>2008/2009 · Essex EUP-116E · 116 cm · Black high gloss · 3 pedals · Bench included | Last tuned 2024</x:v>
       </x:c>
@@ -698,11 +656,9 @@
         <x:v>A privately sold Essex EUP-116E upright from around 2008/2009, designed by Steinway &amp; Sons. The 116 cm piano has a black high-gloss finish, three pedals including a practice pedal, and comes with a bench. The seller describes the tone as warm and balanced with an even touch, notes light normal wear, and says it has always lived indoors. Piano transport is the buyer's responsibility and professional movers are strongly recommended because the instrument weighs about 240 kg.</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2432655350-essex-eup-116e-piano-designed-by-steinway-sons-zwart</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str"/>
       <x:c r="H12" s="14" t="str">
         <x:v>Careful / transparent owner</x:v>
       </x:c>
@@ -720,9 +676,7 @@
       <x:c r="B13" s="14" t="str">
         <x:v>Reserved</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/b69b9cde-ed16-43e8-993e-2b9afa08fb81?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C13" s="14" t="str"/>
       <x:c r="D13" s="14" t="str">
         <x:v>Roland HP603A · Digital · Black high gloss · Like new | Matching bench and music rest included | Light use</x:v>
       </x:c>
@@ -730,11 +684,9 @@
         <x:v>A lightly used Roland HP603A digital piano in excellent condition. The seller highlights a realistic piano sound and touch suitable for beginners through advanced players, with a black high-gloss cabinet, matching bench and music rest. It is described as very well maintained and suitable for home or studio use. The listing is currently reserved.</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435212944-roland-hp603a-digitale-piano-zo-goed-als-nieuw</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str"/>
       <x:c r="H13" s="14" t="str">
         <x:v>Happy / already found a buyer</x:v>
       </x:c>
@@ -752,9 +704,7 @@
       <x:c r="B14" s="14" t="str">
         <x:v>€ 15.000,-</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/bad0cf7f-7448-403a-b15f-fc726879183a?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C14" s="14" t="str"/>
       <x:c r="D14" s="14" t="str">
         <x:v>1910 · Bechstein grand · 184 cm · Full renovation in 2005 · Ivory keys with CITES documentation | Expert report | Recently tuned</x:v>
       </x:c>
@@ -762,11 +712,9 @@
         <x:v>A 1910 Bechstein grand approximately 184 cm long, fully renovated in 2005 with the work documented by certificate. The seller also has CITES documentation for the ivory keys and an expert report, making provenance and legality unusually well documented. Technical condition is described as excellent and positively assessed by Bechstein Europe in Berlin. The black high-gloss case has some scratches, the piano was recently tuned, and the seller is willing to arrange transport.</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435046899-bechsteinvleugel-c-180-2005-gerenoveerd-ivoren-toetsen</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str"/>
       <x:c r="H14" s="14" t="str">
         <x:v>Serious / historical custodian</x:v>
       </x:c>
@@ -784,9 +732,7 @@
       <x:c r="B15" s="14" t="str">
         <x:v>€ 15.500,-</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/1d/1d3d5fb5-10a9-4766-9a1d-a33e0ca8d913?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C15" s="14" t="str"/>
       <x:c r="D15" s="14" t="str">
         <x:v>c.1914 · American Steinway B211 · Major restoration around 2000 with original Steinway parts | Professionally used | Stable climate and tuning</x:v>
       </x:c>
@@ -794,11 +740,9 @@
         <x:v>An American Steinway B211 from around 1914, bought by the current owner around 2000 after a major technical restoration using original Steinway parts. The work included soundboard, strings and action. The owner is a professional classical pianist and says the grand has been carefully maintained in a climate-controlled environment with very stable tuning. It has also been used for house concerts by established classical pianists. The owner is selling because a larger 1922 Grotrian-Steinweg concert grand has become his main instrument.</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2367919409-steinway-sons-b-211-uit-1914-lees-tekst</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str"/>
       <x:c r="H15" s="14" t="str">
         <x:v>Deeply nostalgic / musician-to-musician</x:v>
       </x:c>
@@ -816,9 +760,7 @@
       <x:c r="B16" s="14" t="str">
         <x:v>€ 2.495,-</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/e6842832-f030-4784-8831-7f115e3054bc?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C16" s="14" t="str"/>
       <x:c r="D16" s="14" t="str">
         <x:v>Kawai acoustic upright · Black high gloss · Like new · Bench included | Well maintained | Seller downsizing</x:v>
       </x:c>
@@ -826,11 +768,9 @@
         <x:v>A black high-gloss Kawai acoustic upright in very good condition with a matching piano bench. The seller describes it as rich sounding, well maintained and suitable for beginners or advanced players. It is being sold because of a move to a smaller home, and the seller notes that it should be retuned after transport.</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2434710291-kawai-piano-zwart-hoogglans-met-pianobank</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="str"/>
       <x:c r="H16" s="14" t="str">
         <x:v>Sad / downsizing</x:v>
       </x:c>
@@ -848,9 +788,7 @@
       <x:c r="B17" s="14" t="str">
         <x:v>Bidding</x:v>
       </x:c>
-      <x:c r="C17" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/a40cc2e9-91cd-40d0-be39-a693c670b122?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C17" s="14" t="str"/>
       <x:c r="D17" s="14" t="str">
         <x:v>Roland FP-30 · Digital · Black · Like new | Bench and pedals included | Suitable for home or performance</x:v>
       </x:c>
@@ -858,11 +796,9 @@
         <x:v>A Roland FP-30 digital piano offered with a comfortable bench and pedals. The seller describes it as being in very good condition with everything functioning correctly, highlighting its realistic playing feel and strong sound quality for beginners or more experienced players. The listing is open to bids rather than carrying a fixed price.</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435855393-roland-fp-30-digitale-piano-met-kruk-en-pedalen</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="str"/>
       <x:c r="H17" s="14" t="str">
         <x:v>Friendly / flexible</x:v>
       </x:c>
@@ -880,9 +816,7 @@
       <x:c r="B18" s="14" t="str">
         <x:v>€ 3.650,-</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/b1/b173e945-ddc7-46f4-b48e-70b8f85f202f?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C18" s="14" t="str"/>
       <x:c r="D18" s="14" t="str">
         <x:v>1985 · Yamaha U1A · Acoustic upright · Black high gloss · Workshop prepared | Reduced from €3,950</x:v>
       </x:c>
@@ -890,11 +824,9 @@
         <x:v>A 1985 Yamaha U1A acoustic upright discounted from €3,950 to €3,650. The dealer emphasizes the U1 series' reliability, tuning stability, light playability and clear Yamaha tone, describing this instrument as technically near new after workshop adjustment. It is presented as suitable for children, music students and experienced players alike.</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1499970675-yamaha-u1a-piano-actieprijs-muziekhuis-souman</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str"/>
       <x:c r="H18" s="14" t="str">
         <x:v>Confident / promotional</x:v>
       </x:c>
@@ -912,9 +844,7 @@
       <x:c r="B19" s="14" t="str">
         <x:v>Free</x:v>
       </x:c>
-      <x:c r="C19" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/9232b622-6b44-4afa-9a09-d0bb9ebef537?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C19" s="14" t="str"/>
       <x:c r="D19" s="14" t="str">
         <x:v>Used · White acoustic upright · Approx. 140 cm wide · Unknown make/model | Pickup only</x:v>
       </x:c>
@@ -922,11 +852,9 @@
         <x:v>A free white upright piano of unknown make and model, approximately 1.40 m wide. The seller says it is used but still has life left in it and suggests it could work either as an instrument or as a decorative piece. Exact dimensions are not known and collection is required.</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435855075-mooie-witte-piano-ongeveer-1-40m-breed</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="str"/>
       <x:c r="H19" s="14" t="str">
         <x:v>Casual / please-take-it</x:v>
       </x:c>
@@ -944,9 +872,7 @@
       <x:c r="B20" s="14" t="str">
         <x:v>€ 1.600,-</x:v>
       </x:c>
-      <x:c r="C20" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/e8b5cd04-60e4-4122-9ac7-68cd0bad784d?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C20" s="14" t="str"/>
       <x:c r="D20" s="14" t="str">
         <x:v>Yamaha Tyros 5 · 76 keys · Stand, bench, music rest, manual and flash card included | Small scratch | Pickup in Kortrijk region</x:v>
       </x:c>
@@ -954,11 +880,9 @@
         <x:v>A Yamaha Tyros 5 arranger keyboard with 76 keys, sold with its stand, bench, music rest, manual and flash card. The seller notes a small scratch visible in the photos. Collection is in the Kortrijk region of Belgium and payment is cash on pickup. The seller explicitly states that the €1,600 price is fixed and that unrealistic bids will be ignored.</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435824785-tyros-5-met-76-toetsen</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="str"/>
       <x:c r="H20" s="14" t="str">
         <x:v>Blunt / zero patience</x:v>
       </x:c>
@@ -976,9 +900,7 @@
       <x:c r="B21" s="14" t="str">
         <x:v>€ 65.000,-</x:v>
       </x:c>
-      <x:c r="C21" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/a5/a55fb499-78cd-428c-ba7b-70ab784019ce?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C21" s="14" t="str"/>
       <x:c r="D21" s="14" t="str">
         <x:v>1986 · Hamburg Steinway B211 · 211 cm · Fully revised with original Steinway parts · Black high gloss | 5-year warranty | Nationwide delivery</x:v>
       </x:c>
@@ -986,11 +908,9 @@
         <x:v>A Hamburg-built 1986 Steinway &amp; Sons B211 concert grand restored to near-new condition by an official Steinway dealer. The overhaul used original Steinway parts and included new strings, a new action and refinished black polyester cabinet. The seller highlights the warm singing Hamburg tone, expressive touch, five-year warranty and nationwide delivery.</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1529346333-steinway-sons-b211-vleugel-zo-goed-als-nieuw</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="str"/>
       <x:c r="H21" s="14" t="str">
         <x:v>Prestige / authoritative</x:v>
       </x:c>
@@ -1008,9 +928,7 @@
       <x:c r="B22" s="14" t="str">
         <x:v>Bidding</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/6d465b26-c2c7-40f1-a356-45249e6d467f?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C22" s="14" t="str"/>
       <x:c r="D22" s="14" t="str">
         <x:v>Used · Brown upright · Visible cosmetic damage · Last tuned about 3 years ago | Inherited instrument</x:v>
       </x:c>
@@ -1018,11 +936,9 @@
         <x:v>An inherited Schiedmayer upright with visible cosmetic damage to the cabinet but a sound the seller still considers good. It was last tuned roughly three years ago. Nobody in the seller's household plays piano, so the aim is mainly to find someone who can use and enjoy it rather than keep it unused.</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435818052-schiedmayer-piano</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="str"/>
       <x:c r="H22" s="14" t="str">
         <x:v>Sentimental / generous</x:v>
       </x:c>
@@ -1040,9 +956,7 @@
       <x:c r="B23" s="14" t="str">
         <x:v>€ 52.000,-</x:v>
       </x:c>
-      <x:c r="C23" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/32/32a161a8-8e37-4b18-a9d8-1d2897f45c50?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C23" s="14" t="str"/>
       <x:c r="D23" s="14" t="str">
         <x:v>2019 · Yamaha C6X · 212 cm · Enspire Pro self-playing + Silent system · 440 kg · Black high gloss | Nearly unused | 5-year warranty</x:v>
       </x:c>
@@ -1050,11 +964,9 @@
         <x:v>A 2019 Yamaha C6X grand equipped with both the original Enspire Pro self-playing system and Yamaha Silent functionality. The 212 cm instrument is described as a near-unused demo/consignment example originally sold new by the dealer. The current new price is stated around €87,000, making the €52,000 asking price more than 40% lower. A luxury adjustable bench, five-year warranty and nationwide delivery are included.</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1529329806-yamaha-c6-x-silent-vleugel-zo-goed-als-nieuw</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str"/>
       <x:c r="H23" s="14" t="str">
         <x:v>Luxury / technology-forward</x:v>
       </x:c>
@@ -1072,9 +984,7 @@
       <x:c r="B24" s="14" t="str">
         <x:v>€ 2.950,-</x:v>
       </x:c>
-      <x:c r="C24" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/4971c819-d540-4d96-8ee2-580d48c1645b?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C24" s="14" t="str"/>
       <x:c r="D24" s="14" t="str">
         <x:v>Samick SU-118 DuoPlus · Black high gloss · Like new · Acoustic piano with silent headphone system</x:v>
       </x:c>
@@ -1082,11 +992,9 @@
         <x:v>A Samick SU-118 DuoPlus upright with a Silent system. The seller highlights the piano's solid construction and balanced, rich acoustic tone while emphasizing the practical advantage of switching off the acoustic sound and practicing through headphones without changing the traditional playing feel. It is positioned as a family-friendly acoustic piano for homes where practice noise can become an issue.</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2402215758-prachtige-zwarte-silent-piano</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="str"/>
       <x:c r="H24" s="14" t="str">
         <x:v>Practical / family-aware</x:v>
       </x:c>
@@ -1104,9 +1012,7 @@
       <x:c r="B25" s="14" t="str">
         <x:v>See description</x:v>
       </x:c>
-      <x:c r="C25" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/6a/6a92ea1b-e069-48bb-a562-b7babd4606b1?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C25" s="14" t="str"/>
       <x:c r="D25" s="14" t="str">
         <x:v>Restored Steinway A, O and B grands · Fully renovated in 2026 | 12-year warranty | Free delivery and tuning | Prices €37,950-€57,950</x:v>
       </x:c>
@@ -1114,11 +1020,9 @@
         <x:v>A specialist dealer offers several restored Steinway &amp; Sons grands, including A, O and B models. The available instruments were fully renovated in 2026 and are sold with a 12-year warranty, free delivery and a free tuning. Listed examples range from €37,950 for a Steinway A to €57,950 for a Steinway B, with the exact instrument chosen after viewing the individual photos or showroom stock.</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1529073040-tweedehands-steinway-vleugels-a-b-o</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="str"/>
       <x:c r="H25" s="14" t="str">
         <x:v>Premium / reassuring</x:v>
       </x:c>
@@ -1136,9 +1040,7 @@
       <x:c r="B26" s="14" t="str">
         <x:v>€ 3.500,-</x:v>
       </x:c>
-      <x:c r="C26" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/70f75d67-ea33-4acc-9173-e619e532e6f0?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C26" s="14" t="str"/>
       <x:c r="D26" s="14" t="str">
         <x:v>1972 · Yamaha U1 · Serial 1490197 · Black upright · Tuned/checked twice per year | Conservatory-student owner | Ground floor</x:v>
       </x:c>
@@ -1146,11 +1048,9 @@
         <x:v>A 1972 Japanese Yamaha U1 that has been regularly tuned and checked twice per year. The seller says the instrument was cared for by their son, a conservatory student, and is only being sold because he is moving on to a grand piano. The instrument is already on the ground floor, although transport must be arranged by the buyer. The existing bench is worn and can be taken for free if wanted. The price is explicitly fixed at €3,500.</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435679066-professional-upright-piano</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="str"/>
       <x:c r="H26" s="14" t="str">
         <x:v>Proud parent / milestone sale</x:v>
       </x:c>
@@ -1168,9 +1068,7 @@
       <x:c r="B27" s="14" t="str">
         <x:v>Bidding</x:v>
       </x:c>
-      <x:c r="C27" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/d7c61f2f-127e-4c62-a50d-27d57d65221c?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C27" s="14" t="str"/>
       <x:c r="D27" s="14" t="str">
         <x:v>Less than 1 year old · Roland FP-10 · 88 hammer-action keys · Bluetooth MIDI · 96-note polyphony | Stand, pedal, music rest and power supply included</x:v>
       </x:c>
@@ -1178,11 +1076,9 @@
         <x:v>A nearly new Roland FP-10 set purchased less than a year ago and barely used. The seller originally intended to start learning again but stopped after about four weeks. The piano has 88 PHA-4 hammer-action keys, 96-note polyphony, Roland SuperNATURAL sounds, Twin Piano, split/layer functions, metronome, Bluetooth MIDI and USB connectivity. Stand, pedal, music rest and power supply are included, and a seat can also be taken.</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2435677763-digitale-piano-roland-fp-10-set</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="str"/>
       <x:c r="H27" s="14" t="str">
         <x:v>Self-deprecating / cheerful</x:v>
       </x:c>
@@ -1200,9 +1096,7 @@
       <x:c r="B28" s="14" t="str">
         <x:v>€ 30 / month</x:v>
       </x:c>
-      <x:c r="C28" s="14" t="str">
-        <x:v>https://admarkt-cdn.marktplaats.com/api/v1/icas-mp-pro-admarkt/images/a7/a72d8817-61e9-4d70-bf3b-c813ed3e098d?rule=eps_85</x:v>
-      </x:c>
+      <x:c r="C28" s="14" t="str"/>
       <x:c r="D28" s="14" t="str">
         <x:v>Rental · New digital pianos · Yamaha, Roland and Kawai · Minimum 6 months | Free NL delivery | Purchase option</x:v>
       </x:c>
@@ -1210,11 +1104,9 @@
         <x:v>A nationwide digital-piano rental service offering Yamaha, Roland and Kawai instruments from around €30 per month. Rentals start from six months and are aimed at people who want to begin or resume piano playing without a large upfront purchase. The service advertises free delivery throughout the Netherlands, a purchase option, personal service and only established piano brands.</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/a1208495817-piano-huren-vanaf-30-p-m-koopoptie-gratis-levering-nl</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="str"/>
       <x:c r="H28" s="14" t="str">
         <x:v>Encouraging / low-pressure</x:v>
       </x:c>
@@ -1232,9 +1124,7 @@
       <x:c r="B29" s="14" t="str">
         <x:v>€ 2.000,-</x:v>
       </x:c>
-      <x:c r="C29" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/b305f497-56f0-4f25-9871-fca8fbb914c5?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C29" s="14" t="str"/>
       <x:c r="D29" s="14" t="str">
         <x:v>Yamaha U1 · Black high gloss · Like new / good condition · Light wear | 121×153×61 cm | Ground floor</x:v>
       </x:c>
@@ -1242,11 +1132,9 @@
         <x:v>A black high-gloss Yamaha U1 offered at €2,000. The private seller describes it as well maintained and in good condition, with only light signs of use, a pleasant tone and smooth touch. Dimensions are approximately 121 × 153 × 61 cm and the piano is already on the ground floor for easier removal.</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2426000939-koopje-yamaha-u1-hoogglans-zwart</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str"/>
       <x:c r="H29" s="14" t="str">
         <x:v>Deal-focused / upbeat</x:v>
       </x:c>
@@ -1264,9 +1152,7 @@
       <x:c r="B30" s="14" t="str">
         <x:v>Reserved</x:v>
       </x:c>
-      <x:c r="C30" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/681a356c-a6ef-44cb-ad10-f3b3683e23ac?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C30" s="14" t="str"/>
       <x:c r="D30" s="14" t="str">
         <x:v>Roland FP-30X · Digital · Black · Like new · Bench included | Excellent condition | Selling after buying acoustic piano</x:v>
       </x:c>
@@ -1274,11 +1160,9 @@
         <x:v>A Roland FP-30X digital piano in excellent condition with a bench. The seller highlights its realistic sound and pleasant action and says it works perfectly. It is being sold only because the owner has bought an acoustic piano, which makes this a natural upgrade-driven sale rather than a problem instrument. The listing is currently reserved.</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2432086251-roland-fp-30x-digitale-piano-met-krukje-zo-goed-als-nieuw</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="str"/>
       <x:c r="H30" s="14" t="str">
         <x:v>Excited upgrader</x:v>
       </x:c>
@@ -1296,9 +1180,7 @@
       <x:c r="B31" s="14" t="str">
         <x:v>€ 17.000,-</x:v>
       </x:c>
-      <x:c r="C31" s="14" t="str">
-        <x:v>https://images.marktplaats.com/api/v1/hz-mp-pro-listing/images/6e43ce2d-283b-4ff0-a116-840aefc57c91?rule=ecg_mp_eps%24_85</x:v>
-      </x:c>
+      <x:c r="C31" s="14" t="str"/>
       <x:c r="D31" s="14" t="str">
         <x:v>2004 · Yamaha C3 · 186 cm · Black high gloss · Serial 6075859 · Hamamatsu, Japan | Smoke-free stable room | Adjustable luxury bench</x:v>
       </x:c>
@@ -1306,11 +1188,9 @@
         <x:v>A privately offered 2004 Yamaha C3 grand in exceptional cosmetic and technical condition. The 186 cm instrument was built in Hamamatsu, Japan and has been kept in a smoke-free, stable home environment with regular tuning. The seller describes the soundboard as intact, strings as free of corrosion and the hammers as showing very little playing wear. A height-adjustable luxury bench is included.</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
-        <x:v>Detail page (live)</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/v/muziek-en-instrumenten/piano-s/m2430619965-prachtige-yamaha-c3-vleugel-2004-in-topconditie</x:v>
-      </x:c>
+        <x:v>Provided listing copy</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="str"/>
       <x:c r="H31" s="14" t="str">
         <x:v>Proud / reluctant serious pianist</x:v>
       </x:c>
@@ -1324,7 +1204,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12e827bd209d435f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6c4e6b54e9b408a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1347,11 +1227,9 @@
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="14" t="str">
-        <x:v>Source URL</x:v>
-      </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>https://www.marktplaats.nl/l/muziek-en-instrumenten/piano-s/</x:v>
-      </x:c>
+        <x:v>Source reference removed</x:v>
+      </x:c>
+      <x:c r="B2" s="14"/>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="14" t="str">
@@ -1366,7 +1244,7 @@
         <x:v>Image links</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>One authentic primary Marktplaats image URL is included per row. The live detail-page representation reliably exposes the lead image, but not the full image gallery.</x:v>
+        <x:v>One authentic primary the source marketplace image URL is included per row. The live detail-page representation reliably exposes the lead image, but not the full image gallery.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
@@ -1374,7 +1252,7 @@
         <x:v>English retelling</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Natural English paraphrase of the available Marktplaats seller/listing description. It is not a verbatim translation.</x:v>
+        <x:v>Natural English paraphrase of the available the source marketplace seller/listing description. It is not a verbatim translation.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
@@ -1414,7 +1292,7 @@
         <x:v>Data freshness</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>Retrieved from live Marktplaats pages on 27 August 2026. Availability and prices can change quickly.</x:v>
+        <x:v>Retrieved from live the source marketplace pages on 27 August 2026. Availability and prices can change quickly.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
